--- a/Lasser_Driver_v5/pm22V/pm22V_BOM_digikey.xlsx
+++ b/Lasser_Driver_v5/pm22V/pm22V_BOM_digikey.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,7 +469,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C1,C2</t>
+          <t>pm22V C1,C2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C3,C4,C9,C10</t>
+          <t>pm22V C3,C4,C9,C10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C5,C6</t>
+          <t>pm22V C5,C6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C7,C8</t>
+          <t>pm22V C7,C8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -599,32 +599,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GBPC1510-E4/51</t>
+          <t>GBPC1510W</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>Surge Components</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>pm22V D1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GBPC1510</t>
+          <t>GBPC1510W (GBPC-W)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diode_Bridge_GBPC</t>
+          <t>Diode_Bridge_GBPC-W_PCB</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bridge rect 15A 1000V GBPC bolt</t>
+          <t>Bridge rect 15A 1000V GBPC-W wire-lead PCB+bolt</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>D2,D3</t>
+          <t>pm22V D2,D3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HS1,HS2</t>
+          <t>pm22V HS1,HS2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HS3</t>
+          <t>pm22V HS3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Q1,Q2 (TO-220 iso)</t>
+          <t>pm22V Q1,Q2 (TO-220 iso)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -774,32 +774,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1757255</t>
+          <t>TG-A3500-30-30-0.5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix Contact</t>
+          <t>t-Global</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>pm22V D1/HS3 (thermal)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MSTBA 2,5/3-G-5,08</t>
+          <t>30x30x0.5mm pad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Phoenix_MSTBA_3</t>
+          <t>Hardware (off-PCB)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Term block header 3pos 5.08mm horiz</t>
+          <t>Thermal pad 30x30x0.5mm for GBPC bridge to HS3</t>
         </is>
       </c>
     </row>
@@ -809,32 +809,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>374144-E</t>
+          <t>1729131</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TE/ERNI</t>
+          <t>Phoenix Contact</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>J6</t>
+          <t>pm22V J5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DIN41612 M 3x8+8</t>
+          <t>MKDS 1,5/3-5,08</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DIN41612_M_Power_Male</t>
+          <t>TerminalBlock_MKDS_3_P5.08mm</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIN41612 Type M 24sig+8pwr R/A male</t>
+          <t>Single-piece PCB screw terminal 3pos 5.08mm side-entry</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IRF540NPBF</t>
+          <t>374144-E</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Infineon</t>
+          <t>TE/ERNI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>pm22V J6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IRF540N</t>
+          <t>DIN41612 M 3x8+8</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TO-220-3</t>
+          <t>DIN41612_M_Power_Male</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>N-MOSFET 100V 33A TO-220 (pos pass)</t>
+          <t>DIN41612 Type M 24sig+8pwr R/A male</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IRF9540NPBF</t>
+          <t>IRF540NPBF</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>pm22V Q1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IRF9540N</t>
+          <t>IRF540N</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,42 +904,42 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>P-MOSFET -100V TO-220 (neg pass)</t>
+          <t>N-MOSFET 100V 33A TO-220 (pos pass)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TUW15J15RE</t>
+          <t>IRF9540NPBF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ohmite</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>R2,R3</t>
+          <t>pm22V Q2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15 ohm 15W</t>
+          <t>IRF9540N</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R_Axial_Power_P45.72mm</t>
+          <t>TO-220-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>WW 15ohm 15W axial (soft-start)</t>
+          <t>P-MOSFET -100V TO-220 (neg pass)</t>
         </is>
       </c>
     </row>
@@ -949,32 +949,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RC0805FR-071ML</t>
+          <t>TUW15J15RE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Ohmite</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>R4,R5</t>
+          <t>pm22V R2,R3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>15 ohm 15W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R_0805</t>
+          <t>R_Axial_Power_P45.72mm</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Res 1M 1% 1/8W 0805 (gate bleed)</t>
+          <t>WW 15ohm 15W axial (soft-start)</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RC0805FR-07100KL</t>
+          <t>RC0805FR-071ML</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>R6,R7</t>
+          <t>pm22V R4,R5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Res 100k 1% 1/8W 0805 (gate pull)</t>
+          <t>Res 1M 1% 1/8W 0805 (gate bleed)</t>
         </is>
       </c>
     </row>
@@ -1019,30 +1019,65 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>RC0805FR-07100KL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Yageo</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>pm22V R6,R7</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>100k</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>R_0805</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Res 100k 1% 1/8W 0805 (gate pull)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>CRL1206-FW-R470ELF</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Bourns</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>R8,R9</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>pm22V R8,R9</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>R_1206</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Res 0.47ohm 1% 1/2W 1206 (output series)</t>
         </is>
